--- a/DATA/analysis/page7小结/page7_分层TOP20_2026-08-14.xlsx
+++ b/DATA/analysis/page7小结/page7_分层TOP20_2026-08-14.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,30 +52,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,18 +442,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,35 +471,51 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>楼栋数</t>
+          <t>楼栋</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>体检隐患(点)</t>
+          <t>体检安全
+(每百栋)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>客观密度(每百栋)</t>
+          <t>体检民生
+(每百栋)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>热线诉求(件)</t>
+          <t>热线安全
+(每百栋)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>主观密度(每百栋)</t>
+          <t>热线民生
+(每百栋)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>体检隐患
+(点)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>热线诉求
+(件)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>分层</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -511,23 +534,29 @@
         <v>30</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>370</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>双高</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -542,23 +571,29 @@
         <v>39</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>248.7</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>274.4</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>双高</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -573,23 +608,29 @@
         <v>44</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>261.4</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>双高</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -604,23 +645,29 @@
         <v>66</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>56.1</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>162.1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>177.3</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>双高</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -635,23 +682,29 @@
         <v>94</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>双高</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -666,23 +719,29 @@
         <v>56</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -697,23 +756,29 @@
         <v>78</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>116.7</v>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -728,23 +793,29 @@
         <v>58</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -759,23 +830,29 @@
         <v>78</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>105.1</v>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -790,23 +867,29 @@
         <v>127</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>107</v>
+        <v>61.4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>84.3</v>
+        <v>22.8</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -821,10 +904,10 @@
         <v>48</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -832,12 +915,18 @@
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -852,23 +941,29 @@
         <v>52</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="F13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -883,23 +978,29 @@
         <v>52</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>117.3</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>客观高</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -914,23 +1015,29 @@
         <v>69</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>10.1</v>
       </c>
       <c r="F15" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>653.6</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>501</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>726.1</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -945,23 +1052,29 @@
         <v>84</v>
       </c>
       <c r="D16" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>638.1</v>
+      </c>
+      <c r="H16" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>594</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>707.1</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -976,23 +1089,29 @@
         <v>66</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>13.6</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>484.8</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>372</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>563.6</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1007,23 +1126,29 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>525</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>低置信</t>
         </is>
@@ -1048,17 +1173,23 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>407.7</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>479.5</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1073,23 +1204,29 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>475</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>低置信</t>
         </is>
@@ -1108,25 +1245,56 @@
         <v>28</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>3.6</v>
       </c>
       <c r="F21" s="2" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>410.7</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>主观高</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>图例：蓝色数据条 = 体检（客观·每百栋）；橙色数据条 = 热线（主观·每百栋）；两色同刻度，可横向并排比较。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:E21">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="653.6"/>
+        <color rgb="004472C4"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:G21">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="653.6"/>
+        <color rgb="00ED7D31"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1140,11 +1308,11 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1156,27 +1324,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>体检安全</t>
+          <t>体检安全(点)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>体检民生</t>
+          <t>体检民生(点)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>热线安全</t>
+          <t>热线安全(件)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>热线民生</t>
+          <t>热线民生(件)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>楼栋数</t>
+          <t>楼栋</t>
         </is>
       </c>
     </row>
